--- a/portfolio_backtest_v2_results.xlsx
+++ b/portfolio_backtest_v2_results.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +477,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>BAYRK</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>22136</v>
+        <v>259</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>385.25</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -500,207 +500,207 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>-193.05</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 104.99 | ExpPL: %9.06</t>
+          <t>FinxKüme: -12.03 | ExpPL: %4.30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>BAYRK</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22136</v>
+        <v>259</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>449.00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>104,290.31</t>
+          <t>116,079.11</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P/L: %4.70 | Dev: %-4.36 | Peak: 5.27</t>
+          <t>P/L: %16.55 | Dev: %12.24 | Peak: 432.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>53989</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-229.40</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 536.78 | ExpPL: %11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>PEKGY</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>44567</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>53989</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2.34</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-205.04</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 551.50 | ExpPL: %10.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>PEKGY</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>44567</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>93,643.25</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.83 | Dev: %-20.00 | Peak: 2.34</t>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125,852.19</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %8.84 | Dev: %-2.16 | Peak: 2.59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>53781</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>-247.04</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 551.50 | ExpPL: %10.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>2025-06-20</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>PATEK</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>4676</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-157.50</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 46.43 | ExpPL: %10.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PATEK</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>4676</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (16G)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>96,255.45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.20 | Dev: %-7.75 | Peak: 21.82</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>PEKGY</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>53781</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>113,003.91</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.83 | Dev: %-20.00 | Peak: 2.34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>PATEK</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>27189</v>
+        <v>5643</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -710,67 +710,67 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-186.11</t>
+          <t>-194.90</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 155.88 | ExpPL: %18.31</t>
+          <t>FinxKüme: 46.39 | ExpPL: %10.95</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>KGYO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>27189</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (16G)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>98,583.92</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %2.82 | Dev: %-15.48 | Peak: 3.70</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PATEK</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>5643</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>18.22</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>102,414.92</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-8.99 | Dev: %-19.94 | Peak: 20.02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>KOTON</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>31395</v>
+        <v>7057</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -780,67 +780,67 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-193.55</t>
+          <t>-186.94</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 895.69 | ExpPL: %13.39</t>
+          <t>FinxKüme: -26.65 | ExpPL: %7.48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>KOTON</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>31395</v>
+        <v>7057</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152,081.00</t>
+          <t>102,850.48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>P/L: %54.78 | Dev: %41.39 | Peak: 5.39</t>
+          <t>P/L: %0.83 | Dev: %-6.66 | Peak: 14.98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>TRCAS</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>26231</v>
+        <v>3450</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -850,54 +850,54 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-294.74</t>
+          <t>-160.57</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 259.06 | ExpPL: %16.10</t>
+          <t>FinxKüme: -32.42 | ExpPL: %10.26</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>26231</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>5.18</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>135,216.92</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-10.71 | Dev: %-26.81 | Peak: 5.80</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TRCAS</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3450</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30.78</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>105,823.08</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %3.30 | Dev: %-6.97 | Peak: 29.97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
@@ -906,11 +906,11 @@
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>23514</v>
+        <v>32863</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -920,19 +920,19 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-258.99</t>
+          <t>-207.42</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 710.82 | ExpPL: %11.56</t>
+          <t>FinxKüme: 761.32 | ExpPL: %12.76</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -941,33 +941,33 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>23514</v>
+        <v>32863</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (16G)</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>191,935.50</t>
+          <t>159,187.33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>P/L: %42.43 | Dev: %30.87 | Peak: 8.40</t>
+          <t>P/L: %50.93 | Dev: %38.17 | Peak: 5.39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -976,11 +976,11 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>23434</v>
+        <v>29809</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>-372.80</t>
+          <t>-311.09</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 558.25 | ExpPL: %9.65</t>
+          <t>FinxKüme: 606.53 | ExpPL: %10.48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1011,46 +1011,46 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>23434</v>
+        <v>29809</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200,990.40</t>
+          <t>222,809.27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>P/L: %5.13 | Dev: %-4.52 | Peak: 9.72</t>
+          <t>P/L: %40.45 | Dev: %29.97 | Peak: 7.50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>49140</v>
+        <v>46977</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1060,67 +1060,67 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-394.17</t>
+          <t>-440.75</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 103.18 | ExpPL: %8.73</t>
+          <t>FinxKüme: 105.71 | ExpPL: %7.39</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>MEKAG</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>49140</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>46977</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>262,959.86</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %31.30 | Dev: %22.57 | Peak: 5.96</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>220,412.25</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-0.68 | Dev: %-8.07 | Peak: 5.03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>AVOD</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>71261</v>
+        <v>26554</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1130,67 +1130,67 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-519.14</t>
+          <t>-426.75</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 18.05 | ExpPL: %10.15</t>
+          <t>FinxKüme: 419.50 | ExpPL: %8.29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>AVOD</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>71261</v>
+        <v>26554</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (16G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>402,011.43</t>
+          <t>227,745.92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>P/L: %53.39 | Dev: %43.23 | Peak: 5.15</t>
+          <t>P/L: %3.73 | Dev: %-4.55 | Peak: 9.72</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>A1YEN</t>
+          <t>MEKAG</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>143131</v>
+        <v>55682</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1200,67 +1200,67 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-799.75</t>
+          <t>-448.94</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 77.22 | ExpPL: %8.20</t>
+          <t>FinxKüme: 103.18 | ExpPL: %8.73</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>A1YEN</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>143131</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>363,216.20</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.27 | Dev: %-17.46 | Peak: 2.82</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>MEKAG</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>55682</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>318,526.49</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %40.34 | Dev: %31.62 | Peak: 5.38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>ECZYT</t>
+          <t>AVOD</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>1106</v>
+        <v>86320</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>328.04</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1270,67 +1270,67 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-317.62</t>
+          <t>-631.35</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 40.32 | ExpPL: %6.15</t>
+          <t>FinxKüme: 18.06 | ExpPL: %10.15</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ECZYT</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1106</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>313.27</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>345,467.18</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-4.50 | Dev: %-10.65 | Peak: 347.97</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>AVOD</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>86320</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>374,971.15</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %18.16 | Dev: %8.00 | Peak: 4.55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>74775</v>
+        <v>15045</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1340,67 +1340,67 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-684.23</t>
+          <t>-700.10</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 118.41 | ExpPL: %7.51</t>
+          <t>FinxKüme: 156.89 | ExpPL: %12.36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>74775</v>
+        <v>15045</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>399,308.19</t>
+          <t>461,158.54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P/L: %16.02 | Dev: %8.50 | Peak: 6.03</t>
+          <t>P/L: %23.43 | Dev: %11.08 | Peak: 30.96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>192</v>
+        <v>14991</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>2067.00</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1410,67 +1410,67 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>1,650.46</t>
+          <t>-886.87</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 285.85 | ExpPL: %9.17</t>
+          <t>FinxKüme: 90.56 | ExpPL: %7.57</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>1861.00</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>358,247.84</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.97 | Dev: %-19.13 | Peak: 2067.00</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>14991</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>38.30</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>572,120.11</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %24.51 | Dev: %16.95 | Peak: 37.30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>ECZYT</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>192</v>
+        <v>1743</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>1861.00</t>
+          <t>328.04</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1480,32 +1480,32 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>221.21</t>
+          <t>-790.78</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 380.60 | ExpPL: %11.13</t>
+          <t>FinxKüme: 40.32 | ExpPL: %6.15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>ECZYT</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>192</v>
+        <v>1743</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1711.00</t>
+          <t>313.27</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1515,32 +1515,32 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>328,076.19</t>
+          <t>544,148.56</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-8.06 | Dev: %-19.19 | Peak: 1890.00</t>
+          <t>P/L: %-4.50 | Dev: %-10.65 | Peak: 347.97</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>HDFGS</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>47215</v>
+        <v>117780</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1550,67 +1550,67 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>-644.62</t>
+          <t>-1,083.32</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 203.02 | ExpPL: %13.76</t>
+          <t>FinxKüme: 118.41 | ExpPL: %7.51</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>47215</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>HDFGS</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>117780</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>294,224.87</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.94 | Dev: %-23.70 | Peak: 6.95</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>551,375.53</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %1.73 | Dev: %-5.78 | Peak: 5.12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>HDFGS</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>47016</v>
+        <v>117312</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1620,67 +1620,67 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-578.68</t>
+          <t>-1,093.58</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 117.29 | ExpPL: %8.75</t>
+          <t>FinxKüme: 266.85 | ExpPL: %13.55</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>47016</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>263,911.40</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.92 | Dev: %-18.67 | Peak: 6.26</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HDFGS</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>117312</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>670,930.53</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %22.13 | Dev: %8.58 | Peak: 6.03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>DENGE</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>70942</v>
+        <v>308</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2170.00</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>-520.65</t>
+          <t>1,233.81</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 24.89 | ExpPL: %5.73</t>
+          <t>FinxKüme: 349.34 | ExpPL: %11.20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>DENGE</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>70942</v>
+        <v>308</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>1861.00</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1725,32 +1725,32 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>236,659.73</t>
+          <t>573,275.43</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-9.95 | Dev: %-15.67 | Peak: 3.72</t>
+          <t>P/L: %-14.24 | Dev: %-25.44 | Peak: 2170.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>1386</v>
+        <v>307</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>170.55</t>
+          <t>1861.00</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1760,67 +1760,67 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>-193.56</t>
+          <t>805.78</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 44.04 | ExpPL: %10.44</t>
+          <t>FinxKüme: 380.63 | ExpPL: %11.13</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>1386</v>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>186.80</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>1765.00</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>258,193.44</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %9.53 | Dev: %-0.91 | Peak: 207.50</t>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>541,577.07</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-5.16 | Dev: %-16.28 | Peak: 1890.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>1381</v>
+        <v>306</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>186.80</t>
+          <t>1765.00</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1830,67 +1830,67 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>-293.31</t>
+          <t>406.89</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 43.09 | ExpPL: %9.29</t>
+          <t>FinxKüme: 223.42 | ExpPL: %7.93</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>1381</v>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>229.90</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>1606.00</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>316,563.60</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %23.07 | Dev: %13.79 | Peak: 255.25</t>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>490,860.02</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.01 | Dev: %-16.94 | Peak: 1765.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>15516</v>
+        <v>78439</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>20.40</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1900,67 +1900,67 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>-595.85</t>
+          <t>-974.58</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 159.13 | ExpPL: %7.73</t>
+          <t>FinxKüme: 117.31 | ExpPL: %8.75</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>EKGYO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>15516</v>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>20.44</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (16G)</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>315,916.91</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %0.20 | Dev: %-7.54 | Peak: 20.98</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>78439</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>440,286.64</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.92 | Dev: %-18.67 | Peak: 6.26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>7708</v>
+        <v>14675</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1970,67 +1970,67 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>-588.68</t>
+          <t>-843.86</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 189.42 | ExpPL: %9.02</t>
+          <t>FinxKüme: -6.61 | ExpPL: %7.34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>7708</v>
+        <v>14675</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>49.70</t>
+          <t>34.30</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (16G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>381,732.75</t>
+          <t>501,501.92</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>P/L: %21.28 | Dev: %12.25 | Peak: 48.46</t>
+          <t>P/L: %14.33 | Dev: %6.99 | Peak: 37.04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>96640</v>
+        <v>100518</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2040,67 +2040,67 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>-758.71</t>
+          <t>-993.69</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 125.59 | ExpPL: %10.28</t>
+          <t>FinxKüme: 119.22 | ExpPL: %9.52</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>MEKAG</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>96640</v>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>4.92</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (16G)</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>473,759.16</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %24.56 | Dev: %14.28 | Peak: 4.93</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>100518</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>466,738.60</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-6.55 | Dev: %-16.07 | Peak: 4.99</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>ALVES</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>119938</v>
+        <v>8088</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>57.70</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2110,54 +2110,54 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>-943.45</t>
+          <t>-872.36</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 270.86 | ExpPL: %7.83</t>
+          <t>FinxKüme: 77.00 | ExpPL: %6.63</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ALVES</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>119938</v>
+        <v>8088</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>59.90</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>477,849.04</t>
+          <t>482,629.91</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>P/L: %1.27 | Dev: %-6.56 | Peak: 4.40</t>
+          <t>P/L: %3.81 | Dev: %-2.82 | Peak: 59.45</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
@@ -2166,11 +2166,11 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>1260</v>
+        <v>2504</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>378.75</t>
+          <t>192.60</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2180,67 +2180,67 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>-330.41</t>
+          <t>-605.05</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 55.27 | ExpPL: %12.68</t>
+          <t>FinxKüme: 28.91 | ExpPL: %6.90</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>GUNDG</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>651.00</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (16G)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>818,289.07</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %71.88 | Dev: %59.20 | Peak: 662.00</t>
+      <c r="C51" s="3" t="n">
+        <v>2504</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>178.80</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>446,214.73</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-7.17 | Dev: %-14.07 | Peak: 192.60</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>47491</v>
+        <v>2494</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>178.80</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2250,32 +2250,32 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>-1,617.37</t>
+          <t>-604.33</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 103.17 | ExpPL: %8.24</t>
+          <t>FinxKüme: 35.68 | ExpPL: %8.81</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>47491</v>
+        <v>2494</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>25.20</t>
+          <t>229.90</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2285,32 +2285,32 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1,192,762.32</t>
+          <t>571,619.51</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>P/L: %46.26 | Dev: %38.01 | Peak: 28.00</t>
+          <t>P/L: %28.58 | Dev: %19.77 | Peak: 255.25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>METRO</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>215688</v>
+        <v>28019</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>20.40</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2320,67 +2320,67 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>-2,377.88</t>
+          <t>-1,111.25</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 0.05 | ExpPL: %7.53</t>
+          <t>FinxKüme: 159.20 | ExpPL: %7.73</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>METRO</t>
+          <t>EKGYO</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>215688</v>
+        <v>28019</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (16G)</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1,278,398.99</t>
+          <t>585,551.68</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>P/L: %7.59 | Dev: %0.07 | Peak: 5.90</t>
+          <t>P/L: %2.84 | Dev: %-4.89 | Peak: 20.56</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>ANELE</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>53713</v>
+        <v>1877</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>23.80</t>
+          <t>311.75</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2390,67 +2390,67 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>-2,527.10</t>
+          <t>-773.38</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 32.48 | ExpPL: %12.72</t>
+          <t>FinxKüme: -20.04 | ExpPL: %6.39</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>ANELE</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>53713</v>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>48.60</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1877</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>306.25</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>2,602,703.71</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %104.20 | Dev: %91.49 | Peak: 54.00</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>572,908.21</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.76 | Dev: %-8.15 | Peak: 330.50</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>BIGEN</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>168677</v>
+        <v>67098</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>-5,187.82</t>
+          <t>-1,132.64</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 9.12 | ExpPL: %10.06</t>
+          <t>FinxKüme: 106.54 | ExpPL: %8.22</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BIGEN</t>
+          <t>MANAS</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>168677</v>
+        <v>67098</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2495,32 +2495,32 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3,104,045.32</t>
+          <t>673,854.11</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>P/L: %19.70 | Dev: %9.64 | Peak: 20.52</t>
+          <t>P/L: %18.06 | Dev: %9.84 | Peak: 11.20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>BALSU</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>262830</v>
+        <v>39942</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2530,67 +2530,67 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>-6,185.13</t>
+          <t>-1,315.10</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 368.17 | ExpPL: %10.26</t>
+          <t>FinxKüme: -1.30 | ExpPL: %8.64</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>BALSU</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>262830</v>
+        <v>39942</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2,931,623.42</t>
+          <t>651,626.32</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-5.17 | Dev: %-15.43 | Peak: 13.57</t>
+          <t>P/L: %-2.90 | Dev: %-11.55 | Peak: 16.87</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>BIGEN</t>
+          <t>EDATA</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>74292</v>
+        <v>73051</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2600,67 +2600,67 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>-5,801.95</t>
+          <t>-1,291.83</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 15.67 | ExpPL: %14.82</t>
+          <t>FinxKüme: -17.39 | ExpPL: %6.99</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>74292</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>2,663,361.02</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-8.77 | Dev: %-23.59 | Peak: 40.00</t>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>EDATA</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>73051</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>9.16</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>666,517.02</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %2.69 | Dev: %-4.30 | Peak: 9.40</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>BIGEN</t>
+          <t>BAHKM</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>73981</v>
+        <v>6831</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>97.55</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2670,47 +2670,1062 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>-5,281.61</t>
+          <t>-1,179.78</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 11.34 | ExpPL: %10.72</t>
+          <t>FinxKüme: -38.05 | ExpPL: %12.33</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
+          <t>BAHKM</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>6831</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>136.80</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>931,432.08</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %40.24 | Dev: %27.90 | Peak: 129.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>12017</v>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>77.50</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>-1,748.05</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 75.44 | ExpPL: %4.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>IEYHO</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>12017</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>81.00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>969,682.19</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %4.52 | Dev: %0.36 | Peak: 80.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>OTTO</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>336.50</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>-1,376.05</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: -12.65 | ExpPL: %8.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>OTTO</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>310.25</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>890,356.91</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-7.80 | Dev: %-16.51 | Peak: 343.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>425.75</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>-1,240.22</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 68.73 | ExpPL: %14.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>651.00</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1,356,628.60</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %52.91 | Dev: %38.85 | Peak: 662.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>17.23</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>-2,688.62</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 103.19 | ExpPL: %8.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>MANAS</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2,197,482.22</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %62.51 | Dev: %54.26 | Peak: 25.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>3392</v>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>647.50</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>-3,230.42</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 32.42 | ExpPL: %8.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>GUNDG</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>3392</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>850.00</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2,874,203.18</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %31.27 | Dev: %22.68 | Peak: 870.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>FZLGY</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>193417</v>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>-5,721.73</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 59.29 | ExpPL: %8.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>FZLGY</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>193417</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16.71</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>3,219,812.17</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %12.45 | Dev: %3.78 | Peak: 16.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>135285</v>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>-6,410.29</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 32.46 | ExpPL: %12.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>135285</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>46.30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>6,244,757.71</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %94.54 | Dev: %81.82 | Peak: 46.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>134874</v>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>46.30</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>-12,397.72</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 43.04 | ExpPL: %13.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ANELE</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>134874</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>48.60</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>6,529,368.72</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %4.97 | Dev: %-8.25 | Peak: 54.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
           <t>BIGEN</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>73981</v>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>59.75</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (16G)</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>4,406,242.41</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %65.97 | Dev: %55.25 | Peak: 54.75</t>
+      <c r="C82" s="1" t="n">
+        <v>423159</v>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>15.43</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>-13,033.46</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 9.13 | ExpPL: %10.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>423159</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18.47</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>7,787,081.48</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %19.70 | Dev: %9.64 | Peak: 20.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>EFOR</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>659362</v>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>11.81</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>-15,558.14</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 368.51 | ExpPL: %10.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>EFOR</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>659362</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>12.70</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>8,341,591.34</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %7.54 | Dev: %-2.72 | Peak: 13.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>255719</v>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>32.62</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>-16,645.28</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 12.76 | ExpPL: %13.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>255719</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>9,170,826.95</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %10.36 | Dev: %-2.83 | Peak: 40.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>254744</v>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>-18,298.61</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 11.34 | ExpPL: %10.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>254744</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>44.76</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>11,361,237.72</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %24.33 | Dev: %13.61 | Peak: 40.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>253824</v>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>44.76</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>-22,646.42</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: 11.05 | ExpPL: %11.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>BIGEN</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>253824</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>13,605,773.12</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %20.20 | Dev: %9.12 | Peak: 59.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>HRKET</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>103543</v>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>131.40</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>-26,987.54</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: -16.71 | ExpPL: %9.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>HRKET</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>103543</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>121.00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>12,476,658.05</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-7.91 | Dev: %-17.73 | Peak: 131.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>MSGYO</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>2052080</v>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>6.08</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>-24,941.49</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>FinxKüme: -23.72 | ExpPL: %9.36</t>
         </is>
       </c>
     </row>

--- a/portfolio_backtest_v2_results.xlsx
+++ b/portfolio_backtest_v2_results.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,15 +482,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>259</v>
+        <v>111855</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>385.25</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>-198.37</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -12.03 | ExpPL: %4.30</t>
+          <t>Finansal: 100/100 | ExpPL: %11.00</t>
         </is>
       </c>
     </row>
@@ -517,15 +517,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>259</v>
+        <v>111855</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>449.00</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -535,32 +535,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>116,079.11</t>
+          <t>159,434.37</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P/L: %16.55 | Dev: %12.24 | Peak: 432.00</t>
+          <t>P/L: %59.96 | Dev: %48.95 | Peak: 1.34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>53989</v>
+        <v>2442</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -570,67 +570,67 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>-229.40</t>
+          <t>-224.81</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 536.78 | ExpPL: %11.00</t>
+          <t>Finansal: 44/100 | ExpPL: %10.37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>53989</v>
+        <v>2442</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>74.75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125,852.19</t>
+          <t>181,949.61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P/L: %8.84 | Dev: %-2.16 | Peak: 2.59</t>
+          <t>P/L: %14.56 | Dev: %4.18 | Peak: 69.95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>53781</v>
+        <v>2378</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -640,67 +640,67 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-247.04</t>
+          <t>-263.16</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 551.50 | ExpPL: %10.17</t>
+          <t>Finansal: 79/100 | ExpPL: %7.65</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>PEKGY</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>53781</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>113,003.91</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.83 | Dev: %-20.00 | Peak: 2.34</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>90.69</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>214,973.37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %18.60 | Dev: %10.95 | Peak: 90.69</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>PATEK</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>5643</v>
+        <v>59713</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -710,67 +710,67 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>-194.90</t>
+          <t>-423.36</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 46.39 | ExpPL: %10.95</t>
+          <t>Finansal: 83/100 | ExpPL: %12.46</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>PATEK</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>5643</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>18.22</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>102,414.92</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-8.99 | Dev: %-19.94 | Peak: 20.02</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>KGYO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>59713</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>215,305.37</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %0.56 | Dev: %-11.91 | Peak: 3.60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>KOTON</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>7057</v>
+        <v>1353</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>159.00</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -780,67 +780,67 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-186.94</t>
+          <t>-251.88</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -26.65 | ExpPL: %7.48</t>
+          <t>Finansal: 0/100 | ExpPL: %12.82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>KOTON</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7057</v>
+        <v>1353</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>170.90</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (10G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102,850.48</t>
+          <t>230,513.36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>P/L: %0.83 | Dev: %-6.66 | Peak: 14.98</t>
+          <t>P/L: %7.48 | Dev: %-5.34 | Peak: 184.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>TRCAS</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>3450</v>
+        <v>667</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>29.80</t>
+          <t>344.75</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -850,32 +850,32 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-160.57</t>
+          <t>105.21</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -32.42 | ExpPL: %10.26</t>
+          <t>Finansal: 28/100 | ExpPL: %9.26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TRCAS</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3450</v>
+        <v>667</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>362.00</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -885,32 +885,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105,823.08</t>
+          <t>241,076.30</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P/L: %3.30 | Dev: %-6.97 | Peak: 29.97</t>
+          <t>P/L: %5.00 | Dev: %-4.26 | Peak: 356.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>EMKEL</t>
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>32863</v>
+        <v>3008</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>80.10</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -920,54 +920,54 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-207.42</t>
+          <t>-346.38</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 761.32 | ExpPL: %12.76</t>
+          <t>Finansal: 68/100 | ExpPL: %11.31</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>PEKGY</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>32863</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4.86</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (10G)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159,187.33</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %50.93 | Dev: %38.17 | Peak: 5.39</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>EMKEL</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>70.05</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>209,942.61</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-12.55 | Dev: %-23.85 | Peak: 80.10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -976,11 +976,11 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>29809</v>
+        <v>30206</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>-311.09</t>
+          <t>-408.94</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 606.53 | ExpPL: %10.48</t>
+          <t>Finansal: 99/100 | ExpPL: %11.31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>29809</v>
+        <v>30206</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1025,32 +1025,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>222,809.27</t>
+          <t>249,799.44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>P/L: %40.45 | Dev: %29.97 | Peak: 7.50</t>
+          <t>P/L: %19.42 | Dev: %8.12 | Peak: 8.14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46977</v>
+        <v>8971</v>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1060,32 +1060,32 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-440.75</t>
+          <t>-452.71</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 105.71 | ExpPL: %7.39</t>
+          <t>Finansal: 97/100 | ExpPL: %12.73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>46977</v>
+        <v>8971</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1095,32 +1095,32 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>220,412.25</t>
+          <t>233,401.18</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-0.68 | Dev: %-8.07 | Peak: 5.03</t>
+          <t>P/L: %-6.18 | Dev: %-18.90 | Peak: 27.84</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>26554</v>
+        <v>25451</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1130,67 +1130,67 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-426.75</t>
+          <t>-451.27</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 419.50 | ExpPL: %8.29</t>
+          <t>Finansal: 14/100 | ExpPL: %8.94</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>PEKGY</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>26554</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>8.61</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>227,745.92</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %3.73 | Dev: %-4.55 | Peak: 9.72</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SEKFK</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>25451</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>231,705.64</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-0.33 | Dev: %-9.26 | Peak: 9.47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>55682</v>
+        <v>93053</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-448.94</t>
+          <t>-459.74</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 103.18 | ExpPL: %8.73</t>
+          <t>Finansal: 82/100 | ExpPL: %8.25</t>
         </is>
       </c>
     </row>
@@ -1217,15 +1217,15 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MEKAG</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>55682</v>
+        <v>93053</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1235,32 +1235,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318,526.49</t>
+          <t>249,352.21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>P/L: %40.34 | Dev: %31.62 | Peak: 5.38</t>
+          <t>P/L: %8.03 | Dev: %-0.22 | Peak: 2.99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>AVOD</t>
+          <t>DSTKF</t>
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>86320</v>
+        <v>310</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>801.00</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1270,67 +1270,67 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-631.35</t>
+          <t>545.59</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 18.06 | ExpPL: %10.15</t>
+          <t>Finansal: 13/100 | ExpPL: %8.64</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>AVOD</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>86320</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (10G)</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>374,971.15</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %18.16 | Dev: %8.00 | Peak: 4.55</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>DSTKF</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>721.00</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>223,608.57</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-9.99 | Dev: %-18.63 | Peak: 801.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>15045</v>
+        <v>1708</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>130.77</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-700.10</t>
+          <t>-194.64</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 156.89 | ExpPL: %12.36</t>
+          <t>Finansal: 3/100 | ExpPL: %8.83</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>15045</v>
+        <v>1708</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>153.88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1375,32 +1375,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>461,158.54</t>
+          <t>262,102.08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P/L: %23.43 | Dev: %11.08 | Peak: 30.96</t>
+          <t>P/L: %17.67 | Dev: %8.83 | Peak: 152.08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>14991</v>
+        <v>2324</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>112.70</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1410,67 +1410,67 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>-886.87</t>
+          <t>-336.55</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 90.56 | ExpPL: %7.57</t>
+          <t>Finansal: 52/100 | ExpPL: %12.40</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>IEYHO</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>14991</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>38.30</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (10G)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>572,120.11</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %24.51 | Dev: %16.95 | Peak: 37.30</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2324</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>111.00</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>TRAILING STOP</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>257,111.53</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.51 | Dev: %-13.91 | Peak: 120.70</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>ECZYT</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>1743</v>
+        <v>2315</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>328.04</t>
+          <t>111.00</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1480,67 +1480,67 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>-790.78</t>
+          <t>-367.40</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 40.32 | ExpPL: %6.15</t>
+          <t>Finansal: 51/100 | ExpPL: %12.49</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>ECZYT</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>1743</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>313.27</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>544,148.56</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-4.50 | Dev: %-10.65 | Peak: 347.97</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2315</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>121.00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>279,187.37</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %9.01 | Dev: %-3.48 | Peak: 117.80</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>117780</v>
+        <v>9081</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1550,67 +1550,67 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>-1,083.32</t>
+          <t>-520.87</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 118.41 | ExpPL: %7.51</t>
+          <t>Finansal: 88/100 | ExpPL: %7.92</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>117780</v>
+        <v>9081</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>32.96</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>551,375.53</t>
+          <t>298,190.26</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>P/L: %1.73 | Dev: %-5.78 | Peak: 5.12</t>
+          <t>P/L: %7.22 | Dev: %-0.70 | Peak: 38.30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>117312</v>
+        <v>6280</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1620,137 +1620,137 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-1,093.58</t>
+          <t>-512.87</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 266.85 | ExpPL: %13.55</t>
+          <t>Finansal: 12/100 | ExpPL: %7.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>117312</v>
+        <v>6280</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>56.73</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (10G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>670,930.53</t>
+          <t>355,033.79</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>P/L: %22.13 | Dev: %8.58 | Peak: 6.03</t>
+          <t>P/L: %19.51 | Dev: %12.51 | Peak: 63.03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>ULAS</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>12191</v>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>29.12</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>-678.14</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>Finansal: 61/100 | ExpPL: %11.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>308</v>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>2170.00</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>1,233.81</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 349.34 | ExpPL: %11.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>308</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>1861.00</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>573,275.43</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-14.24 | Dev: %-25.44 | Peak: 2170.00</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ULAS</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>12191</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>33.10</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>402,036.89</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %13.67 | Dev: %2.25 | Peak: 34.92</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>LYDHO</t>
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>307</v>
+        <v>1880</v>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>1861.00</t>
+          <t>213.70</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1760,32 +1760,32 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>805.78</t>
+          <t>-522.61</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 380.63 | ExpPL: %11.13</t>
+          <t>Finansal: 80/100 | ExpPL: %13.91</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>LYDHO</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>307</v>
+        <v>1880</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>1765.00</t>
+          <t>182.30</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1795,32 +1795,32 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>541,577.07</t>
+          <t>341,515.95</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-5.16 | Dev: %-16.28 | Peak: 1890.00</t>
+          <t>P/L: %-14.69 | Dev: %-28.60 | Peak: 213.70</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>306</v>
+        <v>710</v>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>1765.00</t>
+          <t>480.00</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1830,67 +1830,67 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>406.89</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 223.42 | ExpPL: %7.93</t>
+          <t>Finansal: 1/100 | ExpPL: %8.35</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>1606.00</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>490,860.02</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-9.01 | Dev: %-16.94 | Peak: 1765.00</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>TRHOL</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>710</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>546.00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>386,919.03</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %13.75 | Dev: %5.40 | Peak: 547.50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>78439</v>
+        <v>45305</v>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1900,67 +1900,67 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>-974.58</t>
+          <t>-759.48</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 117.31 | ExpPL: %8.75</t>
+          <t>Finansal: 15/100 | ExpPL: %8.98</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>78439</v>
+        <v>45305</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>440,286.64</t>
+          <t>379,945.68</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-9.92 | Dev: %-18.67 | Peak: 6.26</t>
+          <t>P/L: %-1.41 | Dev: %-10.38 | Peak: 8.82</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>14675</v>
+        <v>2226</v>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>170.55</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1970,32 +1970,32 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>-843.86</t>
+          <t>-455.05</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -6.61 | ExpPL: %7.34</t>
+          <t>Finansal: 82/100 | ExpPL: %10.44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>14675</v>
+        <v>2226</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>34.30</t>
+          <t>186.80</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2005,32 +2005,32 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>501,501.92</t>
+          <t>414,530.12</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>P/L: %14.33 | Dev: %6.99 | Peak: 37.04</t>
+          <t>P/L: %9.53 | Dev: %-0.91 | Peak: 207.50</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>100518</v>
+        <v>2218</v>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>186.80</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2040,32 +2040,32 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>-993.69</t>
+          <t>-620.93</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 119.22 | ExpPL: %9.52</t>
+          <t>Finansal: 86/100 | ExpPL: %9.29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>100518</v>
+        <v>2218</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>178.80</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>466,738.60</t>
+          <t>395,164.32</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-6.55 | Dev: %-16.07 | Peak: 4.99</t>
+          <t>P/L: %-4.28 | Dev: %-13.57 | Peak: 192.60</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>8088</v>
+        <v>2209</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>57.70</t>
+          <t>178.80</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2110,54 +2110,54 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>-872.36</t>
+          <t>-594.83</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 77.00 | ExpPL: %6.63</t>
+          <t>Finansal: 86/100 | ExpPL: %8.81</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>8088</v>
+        <v>2209</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>59.90</t>
+          <t>229.90</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (10G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>482,629.91</t>
+          <t>506,238.56</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>P/L: %3.81 | Dev: %-2.82 | Peak: 59.45</t>
+          <t>P/L: %28.58 | Dev: %19.77 | Peak: 255.25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
@@ -2166,11 +2166,11 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>2504</v>
+        <v>2200</v>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>192.60</t>
+          <t>229.90</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>-605.05</t>
+          <t>-552.98</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 28.91 | ExpPL: %6.90</t>
+          <t>Finansal: 86/100 | ExpPL: %11.37</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2201,11 +2201,11 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2504</v>
+        <v>2200</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>178.80</t>
+          <t>196.70</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -2215,32 +2215,32 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>446,214.73</t>
+          <t>431,321.53</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-7.17 | Dev: %-14.07 | Peak: 192.60</t>
+          <t>P/L: %-14.44 | Dev: %-25.81 | Peak: 229.90</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>VERUS</t>
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>2494</v>
+        <v>1803</v>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>178.80</t>
+          <t>239.00</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2250,67 +2250,67 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>-604.33</t>
+          <t>-457.30</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 35.68 | ExpPL: %8.81</t>
+          <t>Finansal: 69/100 | ExpPL: %8.75</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>VERUS</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>2494</v>
+        <v>1803</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>229.90</t>
+          <t>320.00</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>571,619.51</t>
+          <t>575,348.78</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>P/L: %28.58 | Dev: %19.77 | Peak: 255.25</t>
+          <t>P/L: %33.89 | Dev: %25.15 | Peak: 315.25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>EKGYO</t>
+          <t>AKENR</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>28019</v>
+        <v>49726</v>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>20.40</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2320,67 +2320,67 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>-1,111.25</t>
+          <t>-1,131.69</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 159.20 | ExpPL: %7.73</t>
+          <t>Finansal: 82/100 | ExpPL: %14.23</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>EKGYO</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>28019</v>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>20.98</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>AKENR</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>49726</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>11.36</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>585,551.68</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %2.84 | Dev: %-4.89 | Peak: 20.56</t>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>562,625.88</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-1.82 | Dev: %-16.04 | Peak: 11.57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>BALSU</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>1877</v>
+        <v>33689</v>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>311.75</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2390,67 +2390,67 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>-773.38</t>
+          <t>-1,105.66</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -20.04 | ExpPL: %6.39</t>
+          <t>Finansal: 71/100 | ExpPL: %7.74</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>BALSU</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1877</v>
+        <v>33689</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>306.25</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>TRAILING STOP</t>
+          <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>572,908.21</t>
+          <t>549,616.48</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>P/L: %-1.76 | Dev: %-8.15 | Peak: 330.50</t>
+          <t>P/L: %-1.92 | Dev: %-9.66 | Peak: 16.70</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>67098</v>
+        <v>17271</v>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2460,67 +2460,67 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>-1,132.64</t>
+          <t>-1,045.86</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 106.54 | ExpPL: %8.22</t>
+          <t>Finansal: 35/100 | ExpPL: %11.36</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>MANAS</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>67098</v>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>10.08</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>SEGMN</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>17271</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>30.68</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>TRAILING STOP</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>673,854.11</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %18.06 | Dev: %9.84 | Peak: 11.20</t>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>527,768.68</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>P/L: %-3.58 | Dev: %-14.94 | Peak: 35.40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>SEGMN</t>
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>39942</v>
+        <v>17201</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2530,67 +2530,67 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>-1,315.10</t>
+          <t>-1,013.46</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -1.30 | ExpPL: %8.64</t>
+          <t>Finansal: 35/100 | ExpPL: %9.40</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>BALSU</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>39942</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>16.38</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SEGMN</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>17201</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>51.20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>SÜRE DOLDU (10G)</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>651,626.32</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-2.90 | Dev: %-11.55 | Peak: 16.87</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>877,916.37</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %66.88 | Dev: %57.48 | Peak: 46.56</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>PRKME</t>
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>73051</v>
+        <v>42616</v>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2600,32 +2600,32 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>-1,291.83</t>
+          <t>-1,729.03</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -17.39 | ExpPL: %6.99</t>
+          <t>Finansal: 61/100 | ExpPL: %10.78</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>EDATA</t>
+          <t>PRKME</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>73051</v>
+        <v>42616</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2635,32 +2635,32 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>666,517.02</t>
+          <t>899,923.29</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>P/L: %2.69 | Dev: %-4.30 | Peak: 9.40</t>
+          <t>P/L: %2.91 | Dev: %-7.86 | Peak: 21.32</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>BAHKM</t>
+          <t>DSTKF</t>
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>6831</v>
+        <v>910</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>97.55</t>
+          <t>987.50</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2670,67 +2670,67 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>-1,179.78</t>
+          <t>-498.96</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -38.05 | ExpPL: %12.33</t>
+          <t>Finansal: 9/100 | ExpPL: %6.11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BAHKM</t>
+          <t>DSTKF</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>6831</v>
+        <v>910</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>136.80</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (10G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>931,432.08</t>
+          <t>1,225,544.04</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>P/L: %40.24 | Dev: %27.90 | Peak: 129.00</t>
+          <t>P/L: %36.71 | Dev: %30.60 | Peak: 1487.00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>12017</v>
+        <v>2877</v>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>77.50</t>
+          <t>425.75</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2740,32 +2740,32 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>-1,748.05</t>
+          <t>-1,788.48</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 75.44 | ExpPL: %4.16</t>
+          <t>Finansal: 83/100 | ExpPL: %14.06</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>12017</v>
+        <v>2877</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>651.00</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2775,32 +2775,32 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>969,682.19</t>
+          <t>1,867,392.67</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>P/L: %4.52 | Dev: %0.36 | Peak: 80.60</t>
+          <t>P/L: %52.91 | Dev: %38.85 | Peak: 662.00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>DSTKF</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>2880</v>
+        <v>1077</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>336.50</t>
+          <t>1731.00</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2810,67 +2810,67 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>-1,376.05</t>
+          <t>-622.91</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: -12.65 | ExpPL: %8.71</t>
+          <t>Finansal: 18/100 | ExpPL: %10.20</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>OTTO</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>2880</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>310.25</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>890,356.91</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-7.80 | Dev: %-16.51 | Peak: 343.00</t>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>DSTKF</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1077</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>1844.00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>SÜRE DOLDU (10G)</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1,981,393.12</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>P/L: %6.53 | Dev: %-3.67 | Peak: 1840.00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>2090</v>
+        <v>4666</v>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>425.75</t>
+          <t>424.50</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2880,32 +2880,32 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>-1,240.22</t>
+          <t>-3,285.32</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 68.73 | ExpPL: %14.06</t>
+          <t>Finansal: 44/100 | ExpPL: %9.66</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>2090</v>
+        <v>4666</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>651.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1,356,628.60</t>
+          <t>2,092,215.28</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>P/L: %52.91 | Dev: %38.85 | Peak: 662.00</t>
+          <t>P/L: %6.01 | Dev: %-3.65 | Peak: 447.00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>78735</v>
+        <v>40195</v>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>52.05</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2950,67 +2950,67 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>-2,688.62</t>
+          <t>-4,118.73</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 103.19 | ExpPL: %8.24</t>
+          <t>Finansal: 43/100 | ExpPL: %14.18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MANAS</t>
+          <t>MARKA</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>78735</v>
+        <v>40195</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>53.10</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>SÜRE DOLDU (10G)</t>
+          <t>TRAILING STOP</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2,197,482.22</t>
+          <t>2,125,967.00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>P/L: %62.51 | Dev: %54.26 | Peak: 25.98</t>
+          <t>P/L: %2.02 | Dev: %-12.17 | Peak: 59.00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>VERUS</t>
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>3392</v>
+        <v>4428</v>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>647.50</t>
+          <t>480.00</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -3020,32 +3020,32 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>-3,230.42</t>
+          <t>-3,723.88</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 32.42 | ExpPL: %8.60</t>
+          <t>Finansal: 61/100 | ExpPL: %9.32</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>GUNDG</t>
+          <t>VERUS</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3392</v>
+        <v>4428</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>850.00</t>
+          <t>505.00</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3055,32 +3055,32 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2,874,203.18</t>
+          <t>2,227,943.84</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>P/L: %31.27 | Dev: %22.68 | Peak: 870.00</t>
+          <t>P/L: %5.21 | Dev: %-4.11 | Peak: 500.00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>FZLGY</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>193417</v>
+        <v>93610</v>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>23.80</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -3090,32 +3090,32 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>-5,721.73</t>
+          <t>-4,429.93</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 59.29 | ExpPL: %8.67</t>
+          <t>Finansal: 76/100 | ExpPL: %12.02</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>FZLGY</t>
+          <t>ANELE</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>193417</v>
+        <v>93610</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>50.90</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3125,32 +3125,32 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>3,219,812.17</t>
+          <t>4,750,789.72</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>P/L: %12.45 | Dev: %3.78 | Peak: 16.66</t>
+          <t>P/L: %113.87 | Dev: %101.85 | Peak: 46.30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>ANELE</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>135285</v>
+        <v>117071</v>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>23.80</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -3160,32 +3160,32 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>-6,410.29</t>
+          <t>-9,453.16</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>FinxKüme: 32.46 | ExpPL: %12.72</t>
+          <t>Finansal: 70/100 | ExpPL: %9.57</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ANELE</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>135285</v>
+        <v>117071</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>46.30</t>
+          <t>55.45</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3195,537 +3195,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>6,244,757.71</t>
+          <t>6,469,150.70</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>P/L: %94.54 | Dev: %81.82 | Peak: 46.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>ANELE</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>134874</v>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>46.30</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-12,397.72</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 43.04 | ExpPL: %13.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>ANELE</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>134874</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>48.60</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>6,529,368.72</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %4.97 | Dev: %-8.25 | Peak: 54.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>423159</v>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>15.43</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-13,033.46</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 9.13 | ExpPL: %10.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>423159</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>18.47</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>7,787,081.48</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %19.70 | Dev: %9.64 | Peak: 20.52</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="n">
-        <v>659362</v>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>11.81</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-15,558.14</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 368.51 | ExpPL: %10.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>659362</v>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>12.70</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>8,341,591.34</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %7.54 | Dev: %-2.72 | Peak: 13.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="n">
-        <v>255719</v>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>-16,645.28</t>
-        </is>
-      </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 12.76 | ExpPL: %13.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v>255719</v>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>9,170,826.95</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %10.36 | Dev: %-2.83 | Peak: 40.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="n">
-        <v>254744</v>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-18,298.61</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 11.34 | ExpPL: %10.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v>254744</v>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>44.76</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>SÜRE DOLDU (10G)</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>11,361,237.72</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %24.33 | Dev: %13.61 | Peak: 40.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="n">
-        <v>253824</v>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>44.76</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>-22,646.42</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: 11.05 | ExpPL: %11.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>BIGEN</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>253824</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>53.80</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>13,605,773.12</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>P/L: %20.20 | Dev: %9.12 | Peak: 59.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>HRKET</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="n">
-        <v>103543</v>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>131.40</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-26,987.54</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: -16.71 | ExpPL: %9.81</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>HRKET</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>103543</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>121.00</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>TRAILING STOP</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>12,476,658.05</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>P/L: %-7.91 | Dev: %-17.73 | Peak: 131.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>MSGYO</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="n">
-        <v>2052080</v>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>6.08</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-24,941.49</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>FinxKüme: -23.72 | ExpPL: %9.36</t>
+          <t>P/L: %36.64 | Dev: %27.08 | Peak: 52.40</t>
         </is>
       </c>
     </row>
